--- a/Hoadon/HD2026/HDVao/5/3502323472_HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HD2026/HDVao/5/3502323472_HDDienTuDaCapMa.xlsx
@@ -213,7 +213,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Từ ngày 01/05/2026 đến ngày 06/05/2026</t>
+          <t>Từ ngày 01/05/2026 đến ngày 07/05/2026</t>
         </is>
       </c>
     </row>
@@ -311,6 +311,89 @@
       <c r="S6" s="3" t="inlineStr">
         <is>
           <t>Kết quả kiểm tra hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C26TVH</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3502293066</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ TIN HỌC VIETTECH</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>3502323472</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẦU TƯ THƯƠNG MẠI NGHĨA HÀ</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Số 234 Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>6870371.0</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>549629.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>7420000.0</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
         </is>
       </c>
     </row>
